--- a/MiniTemplate/Datas/base.xlsx
+++ b/MiniTemplate/Datas/base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62481688-903E-4DC7-A9C4-2709A8B312D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A96E1E6-5A7C-4B6C-9D2A-CB2CADCEF7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3588" yWindow="3168" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_simulation_coin]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rewardScale</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,7 +118,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_heart]</t>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_simulation_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_heart]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -457,16 +458,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="64.125" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,10 +484,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -503,10 +504,10 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -523,10 +524,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -543,10 +544,10 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>101</v>
       </c>
@@ -554,41 +555,41 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>102</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
@@ -597,22 +598,22 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>

--- a/MiniTemplate/Datas/base.xlsx
+++ b/MiniTemplate/Datas/base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A96E1E6-5A7C-4B6C-9D2A-CB2CADCEF7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C228FADF-BDF2-4FC8-B75D-4F197ED892CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Lottery/SpriteAtlas.spriteatlasv2[icon_lottery_coin]</t>
-  </si>
-  <si>
     <t>基础货币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -118,11 +115,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_simulation_coin]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_heart]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -141,6 +142,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -458,16 +460,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="51.875" customWidth="1"/>
-    <col min="5" max="5" width="64.125" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -507,7 +509,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -527,7 +529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -547,7 +549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>101</v>
       </c>
@@ -555,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>25</v>
@@ -564,56 +566,56 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>102</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F7">
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>

--- a/MiniTemplate/Datas/base.xlsx
+++ b/MiniTemplate/Datas/base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C228FADF-BDF2-4FC8-B75D-4F197ED892CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAF7F66-9633-4E2F-8E92-18598678DD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -124,6 +124,18 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转盘币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽奖货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_wheel_coin]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,16 +472,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="64.125" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -509,7 +521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -529,7 +541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -549,7 +561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>101</v>
       </c>
@@ -566,7 +578,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>102</v>
       </c>
@@ -583,7 +595,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>103</v>
       </c>
@@ -600,22 +612,34 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>

--- a/MiniTemplate/Datas/base.xlsx
+++ b/MiniTemplate/Datas/base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAF7F66-9633-4E2F-8E92-18598678DD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B771F4A-B68E-4F45-8CBF-578AA0037667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -136,6 +136,18 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_wheel_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秘匣币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽奖货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_secret_box_coin]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,16 +484,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="51.875" customWidth="1"/>
-    <col min="5" max="5" width="64.125" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -521,7 +533,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -541,7 +553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -561,7 +573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>101</v>
       </c>
@@ -578,7 +590,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>102</v>
       </c>
@@ -595,7 +607,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>103</v>
       </c>
@@ -612,7 +624,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>104</v>
       </c>
@@ -629,17 +641,29 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>105</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
